--- a/dados_excel/players.xlsx
+++ b/dados_excel/players.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O644"/>
+  <dimension ref="A1:O665"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="24" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -828,6 +828,11 @@
           <t>filiceta#2107</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>dark#2107</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -855,6 +860,11 @@
           <t>entropy#fermi</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spx#six7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4459,6 +4469,11 @@
           <t>Zuhazana#2004</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>BBL lovers rock#1912</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4557,9 +4572,14 @@
           <t>ufrj_minerva</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ufrj_minerva</t>
+          <t>minerva_artemis</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8799,6 +8819,11 @@
           <t>risk it all#szz</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Stalkzin#szz</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16836,6 +16861,11 @@
           <t>RACFLU#2812</t>
         </is>
       </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>rac#manu</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -16875,9 +16905,14 @@
           <t>a2e_uff</t>
         </is>
       </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>a2e_uff</t>
+          <t>a2e_uff_shadows</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -16888,6 +16923,11 @@
       <c r="L567" t="inlineStr">
         <is>
           <t>A2E Borrachinha#UFF</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>Snoopy#D0GGY</t>
         </is>
       </c>
     </row>
@@ -16951,6 +16991,11 @@
           <t>a2e_uff</t>
         </is>
       </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>a2e_uff</t>
+        </is>
+      </c>
       <c r="I570" t="inlineStr">
         <is>
           <t>pdRsfXh651uh4CZQd0fw9odXzapO0ncZnyXfwybzgMFl8XMthzJWeXl33l0k6by9eb85rmaRvFnDtg</t>
@@ -18809,6 +18854,11 @@
           <t>ufrj_minerva</t>
         </is>
       </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
       <c r="I644" t="inlineStr">
         <is>
           <t>6VmRqgEcADA3-FPKNyHudktkAmRCQ24f4-7qULqSetlt4BwhJOMPordrLxy5QW_H7xCbO87n8YDM4w</t>
@@ -18817,6 +18867,573 @@
       <c r="L644" t="inlineStr">
         <is>
           <t>Zerando#BAGRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>loverman</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>t08VZ3J89mOM5yLqJpgOe_xyYY5GskO8DAvT18IkG9iMnLESQhAeq-EcnQHSI7T8Z5sNRNO-huvKZQ</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>loverman#yzz</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>lpWxQCvw4rkk9GfEF-1WUoiuEhqGc9fXGYLDvnjv-BRasolYpyUlcrULHKHYqwNks8kZIbFPBtiJig</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>DG  叶#Deus</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>draCo</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>ufrj_minerva</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>APM9XNdFLPZ0XIsxhQtKwlURG6MwycOF4EA0OZgJy-DCHEHh4vZmPDsjOjw2mUkEsJ-73BZEbseMrQ</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>draCo#044</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>salem</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>wolf_gaming</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>wolf_gaming</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>mhUL_Fn0WJcLpLYtjzvnF2zVpyxhkZAPX0ljZpHbQeU25c8SzH-iu8arXjuyMcH7N48AHDXp2sgFEA</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>salem#rosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>raining stars</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>amjD_6OtKf_MwccutUhwOMy4jLU803YXM7JslAaEcR0-v1vQyB9ukp0s9CfDvDnIh-_d3I2_Hsr_oA</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>raining stars#yuni</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>dudinhal</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>oZf3TOi8xYXZTqpYzgw2eM8zmWyHuiHYUHHEYslpw81Q7OtfHrBWYXUS9aL1FGJ5N9870U6UuTi6ow</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>chocolate n mint#lwykm</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Mey</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>chLoZYtUyKY0CiH_AznDtIu9nU2fEOArkDqU2kT7WwjhyDafLkI5AUtRygkEX78T7nsW8WMP_oJllg</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>美 Mey#余家贤</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>DavyJones</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Cl7a6Q8hzvSHU3T84nMR0vxVt6q7BYF0Bi3Zf5e128gLkuMSsBaKUMp0bqW9xo0fK4pv75X-VXOPbA</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>DavyJonesAndThe6#momo</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>kissa</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>minerva_artemis</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>BudR61mnu-MK5jvQyvZAUK_WNzWd3Vza4kvbeBtYJ0orRfRl5YSsEdwiI54OTcb6leXH9XlCTf3cDw</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>kissa#fada</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>GalinhaMamifera</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>K2nP5lhGeWcXKEoVzO1O-lICjLS4f2l_7X5U2uamQbAIxx3Jgkj_95sVV_ip-8TjWGrzQ1Yo4E049w</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>GalinhaMamifera#prota</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>drk</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>RRuFlSaUvwSAbsU0VZWUccWHztIDpZw_Q0uTHOpnzEfsCQUfxdzlNn3j5BEPEcQHEgwmSnmSfIzK1w</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>drk#calmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>gL X</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>uojDz5vQxGiQKP7g90cebiqhnWN3EL1qBNljUxvSQvAf4k3oDTwnq6KQviDPThkPSSWfxssA0NrQ1w</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>gL X#fate</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Hast</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>1_hQmAKryuKCb0iUe3VrPTRdSVQaukeApnXQjOJSgxKreJmPhiARIkJ_Ho1adcFAVz2rSqsVkq3b3g</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Hдsτ#puro</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ferRomantica</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>J7-IUFRYPuKeg94Dw37IP77y47Hfs3e281XUhN2sJVs6o4DYtcDo9APe7RaJq9YWPHNiY5kf0j4Uxw</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>ferRomantica#dsz</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Kafaja</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>a2e_uff_shadows</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>yhYgxQ1ptlFWqeif57GjQXFcHNTNyEgzDsMoSmfiOExbq79qnHdP4JQOQu9NIAHf_KeLqIviM0-uYw</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Kafaja#hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Fael</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>DQeT0eDF3SHvDHlHce_p-IHH-ZzGorImLBwcd6sw5Zl9VqZ6xLI1isr8cQk5w4cbVRgvUnKxsxDKxQ</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Fael#Love</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>rahg</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>PX9Q4jAJAD7qzjhaKpI9OaR1V2nzy4nP4k4VobAgj4-r61FFnxlSMgPmAEef3mjFxhvewv8nb4IRnA</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>rahg#Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>aQc</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>LXqUks3cWUhxyVuwWNNPZgLi7WDOmgePhEMh2SqbN73VLZVEyjNYefabtZEvCxXkndvQyTc1NyOxhw</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>aQc#0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Eraj</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Q0mKW1c7ZtJuYT_LL9Ub4l7weqUWxxYLH9UGHKmAU-3eMzxCseuORCE2e9UxPqza2Z1xjQPXY9qHrg</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>SHF Eraj#Adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Kossar Osako</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>KviH96suaczjX80gkl5o8zlBiOub18_Saz0VMFcyCxoTFrJo5OeP3SsSHRoH4PkfmS2-kBqgsF6MnQ</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Kossar Osako#poger</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>lucKZin</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>sheriff_iff</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>IFQTwyLBTjVhxuivh4J05ik0JSim3r6W0PbWtkrT4y3L_f9fzMLCtCmc4b74IXvnmjT90o6RmMQkhg</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>lucKZin#KLZ</t>
         </is>
       </c>
     </row>

--- a/dados_excel/players.xlsx
+++ b/dados_excel/players.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -805,7 +805,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Filiceta</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>spx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Queijo Coallho</t>
+          <t>Marelo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
